--- a/r4-ELGA-IV-Herzinsuffizienz-main/StructureDefinition-Folgedokumentation-hi.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-main/StructureDefinition-Folgedokumentation-hi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T14:23:32+00:00</t>
+    <t>2025-01-28T07:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-main/StructureDefinition-Folgedokumentation-hi.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-main/StructureDefinition-Folgedokumentation-hi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T07:27:13+00:00</t>
+    <t>2025-01-29T13:57:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-main/StructureDefinition-Folgedokumentation-hi.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-main/StructureDefinition-Folgedokumentation-hi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T13:57:17+00:00</t>
+    <t>2025-02-19T08:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-main/StructureDefinition-Folgedokumentation-hi.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-main/StructureDefinition-Folgedokumentation-hi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T08:14:55+00:00</t>
+    <t>2025-02-27T14:20:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-main/StructureDefinition-Folgedokumentation-hi.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-main/StructureDefinition-Folgedokumentation-hi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:20:34+00:00</t>
+    <t>2025-02-27T14:24:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-main/StructureDefinition-Folgedokumentation-hi.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-main/StructureDefinition-Folgedokumentation-hi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:24:03+00:00</t>
+    <t>2025-02-28T10:03:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-main/StructureDefinition-Folgedokumentation-hi.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-main/StructureDefinition-Folgedokumentation-hi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:03:13+00:00</t>
+    <t>2025-03-13T12:24:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-main/StructureDefinition-Folgedokumentation-hi.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-main/StructureDefinition-Folgedokumentation-hi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-13T12:24:38+00:00</t>
+    <t>2025-03-20T15:07:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
